--- a/config/auto_configs/2024_Hyundai_Hyundai_Tucson(NX4A)_G 2.5 GDI THETA3.xlsx
+++ b/config/auto_configs/2024_Hyundai_Hyundai_Tucson(NX4A)_G 2.5 GDI THETA3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_10003</t>
+          <t>HMA_HK_01076</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C161487</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_HK_00970</t>
+          <t>HMA_HK_01076</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C110913</t>
+          <t>C161688</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_HK_00970</t>
+          <t>HMA_10010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C111401</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C120001</t>
+          <t>C110913</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C120102</t>
+          <t>C111401</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C120202</t>
+          <t>C120001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C120301</t>
+          <t>C120102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C120402</t>
+          <t>C120202</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C120502</t>
+          <t>C120301</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C120601</t>
+          <t>C120402</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C120702</t>
+          <t>C120502</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C120802</t>
+          <t>C120601</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C120901</t>
+          <t>C120702</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C121002</t>
+          <t>C120802</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C121102</t>
+          <t>C120901</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C125901</t>
+          <t>C121002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C126002</t>
+          <t>C121102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C126104</t>
+          <t>C125901</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C126402</t>
+          <t>C126002</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C128208</t>
+          <t>C126104</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>C126402</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C128504</t>
+          <t>C128208</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C128601</t>
+          <t>C128302</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C135301</t>
+          <t>C128504</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C135501</t>
+          <t>C128601</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>C135301</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C135B08</t>
+          <t>C135501</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C135C08</t>
+          <t>C135801</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C137801</t>
+          <t>C135B08</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>C135C08</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C152001</t>
+          <t>C137801</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C152601</t>
+          <t>C150301</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C152701</t>
+          <t>C152001</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C160696</t>
+          <t>C152601</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C161108</t>
+          <t>C152701</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C161208</t>
+          <t>C160696</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C161308</t>
+          <t>C161108</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C161408</t>
+          <t>C161208</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C161688</t>
+          <t>C161308</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C161C86</t>
+          <t>C161408</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C162308</t>
+          <t>C161688</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C162708</t>
+          <t>C161C86</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C162A08</t>
+          <t>C162308</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C162A87</t>
+          <t>C162708</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C162E04</t>
+          <t>C162A08</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C163808</t>
+          <t>C162A87</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C163883</t>
+          <t>C162E04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C163886</t>
+          <t>C163808</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C163887</t>
+          <t>C163883</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C164308</t>
+          <t>C163886</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C164808</t>
+          <t>C163887</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C164908</t>
+          <t>C164308</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C165008</t>
+          <t>C164808</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C165683</t>
+          <t>C164908</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C165686</t>
+          <t>C165008</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C165A87</t>
+          <t>C165683</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C168708</t>
+          <t>C165686</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C168808</t>
+          <t>C165A87</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C168882</t>
+          <t>C168708</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C168883</t>
+          <t>C168808</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C168886</t>
+          <t>C168882</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C168887</t>
+          <t>C168883</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C169508</t>
+          <t>C168886</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C16B408</t>
+          <t>C168887</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>C16B687</t>
+          <t>C169508</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>C16B808</t>
+          <t>C16B408</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C16B882</t>
+          <t>C16B687</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C16B883</t>
+          <t>C16B808</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C16B887</t>
+          <t>C16B882</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C171004</t>
+          <t>C16B883</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C171055</t>
+          <t>C16B887</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>C180608</t>
+          <t>C171004</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>C181208</t>
+          <t>C171055</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C181482</t>
+          <t>C180608</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C181483</t>
+          <t>C181208</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>C181486</t>
+          <t>C181482</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C181487</t>
+          <t>C181483</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>C181708</t>
+          <t>C181486</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>C181787</t>
+          <t>C181487</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C181887</t>
+          <t>C181708</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>C183782</t>
+          <t>C181787</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C183783</t>
+          <t>C181887</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>C183787</t>
+          <t>C183782</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>C183986</t>
+          <t>C183783</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>C184082</t>
+          <t>C183787</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>C184083</t>
+          <t>C183986</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>C184087</t>
+          <t>C184082</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C184783</t>
+          <t>C184083</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C184787</t>
+          <t>C184087</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C186982</t>
+          <t>C184783</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C186983</t>
+          <t>C184787</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C186987</t>
+          <t>C186982</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C220277</t>
+          <t>C186983</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>C222001</t>
+          <t>C186987</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>C222071</t>
+          <t>C220277</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C222074</t>
+          <t>C222001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C222077</t>
+          <t>C222071</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>C222094</t>
+          <t>C222074</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C222401</t>
+          <t>C222077</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C222471</t>
+          <t>C222094</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C222474</t>
+          <t>C222401</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C222477</t>
+          <t>C222471</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C222494</t>
+          <t>C222474</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C222808</t>
+          <t>C222477</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>C222908</t>
+          <t>C222494</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C224077</t>
+          <t>C222808</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C224494</t>
+          <t>C222908</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>C224077</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C240201</t>
+          <t>C224494</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C241601</t>
+          <t>C238001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C241611</t>
+          <t>C240201</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>C241612</t>
+          <t>C241601</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C241613</t>
+          <t>C241611</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>C241671</t>
+          <t>C241612</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>C241701</t>
+          <t>C241613</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>C241711</t>
+          <t>C241671</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C241712</t>
+          <t>C241701</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C241713</t>
+          <t>C241711</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C241771</t>
+          <t>C241712</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C241877</t>
+          <t>C241713</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C241977</t>
+          <t>C241771</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3182,20 +3182,702 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HMA_HK_00970</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>C241877</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HMA_HK_00970</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>C241977</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>SRS</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HMA_10003</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
         <is>
           <t>HMA_10042</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HMA_HK_01081</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HMA_HK_01049</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HMA_HK_00975</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HMA_HK_00976</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HMA_HK_01085</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HMA_HK_01086</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HMA_HK_00980</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HMA_HK_01018</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HMA_HK_01966</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HMA_HK_01090</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HMA_HK_01091</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HMA_HK_01936</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HMA_HK_01093</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HMA_HK_01094</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HMA_HK_01095</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HMA_HK_01096</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HMA_HK_01097</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HMA_HK_01098</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HMA_HK_01099</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HMA_HK_01100</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>RCR-L</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HMA_HK_01101</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>RCR-R</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HMA_HK_01102</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HMA_HK_01103</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HMA_HK_01104</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HMA_HK_01105</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HMA_HK_01106</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMA_HK_01107</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HMA_HK_01108</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>00</t>
         </is>
